--- a/results/tables/Temperatura_linfocitos_resultados.xlsx
+++ b/results/tables/Temperatura_linfocitos_resultados.xlsx
@@ -594,7 +594,7 @@
     <t xml:space="preserve">Input file</t>
   </si>
   <si>
-    <t xml:space="preserve">Registros_Lym_y_Temperaturas_ensayo_DVB.xlsx</t>
+    <t xml:space="preserve">Temperaturas.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Animals (challenge)</t>
@@ -606,7 +606,7 @@
     <t xml:space="preserve">Withdrawn animals excluded</t>
   </si>
   <si>
-    <t xml:space="preserve">5452, 5434, 4906, 5442</t>
+    <t xml:space="preserve">5451, 5452, 5434, 4906, 5442</t>
   </si>
   <si>
     <t xml:space="preserve">Relabelled rows</t>
@@ -20901,67 +20901,67 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C3" t="n">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="D3" t="s">
         <v>157</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C4" t="n">
-        <v>5.24</v>
+        <v>5.39</v>
       </c>
       <c r="D4" t="s">
         <v>157</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C5" t="n">
-        <v>6.65</v>
+        <v>6.27</v>
       </c>
       <c r="D5" t="s">
         <v>157</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C6" t="n">
-        <v>7.05</v>
+        <v>6.04</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -20972,101 +20972,101 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>5.31</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>4.25</v>
+        <v>5.19</v>
       </c>
       <c r="D8" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C9" t="n">
-        <v>4.06</v>
+        <v>5.11</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C10" t="n">
-        <v>5.05</v>
+        <v>5.84</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E10" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C11" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C12" t="n">
-        <v>5.5</v>
+        <v>5.24</v>
       </c>
       <c r="D12" t="s">
         <v>157</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -21074,27 +21074,27 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" t="n">
-        <v>5.19</v>
+        <v>4.94</v>
       </c>
       <c r="D13" t="s">
         <v>157</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>159</v>
       </c>
       <c r="C14" t="n">
-        <v>4.94</v>
+        <v>4.65</v>
       </c>
       <c r="D14" t="s">
         <v>157</v>
@@ -21105,53 +21105,53 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C15" t="n">
-        <v>6.08</v>
+        <v>4.56</v>
       </c>
       <c r="D15" t="s">
         <v>157</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C16" t="n">
-        <v>6.4</v>
+        <v>4.18</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C17" t="n">
-        <v>6.44</v>
+        <v>6.65</v>
       </c>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -21159,81 +21159,81 @@
         <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C18" t="n">
-        <v>4.95</v>
+        <v>6.08</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C19" t="n">
-        <v>6.01</v>
+        <v>5.33</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C20" t="n">
-        <v>6.38</v>
+        <v>4.81</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C21" t="n">
-        <v>5.45</v>
+        <v>5.81</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>157</v>
       </c>
       <c r="E21" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C22" t="n">
-        <v>5.39</v>
+        <v>7.05</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21241,19 +21241,19 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C23" t="n">
-        <v>5.11</v>
+        <v>6.4</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -21261,44 +21261,44 @@
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C24" t="n">
-        <v>4.65</v>
+        <v>5.81</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25" t="n">
-        <v>5.33</v>
+        <v>5.55</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
         <v>161</v>
       </c>
       <c r="C26" t="n">
-        <v>5.81</v>
+        <v>5.07</v>
       </c>
       <c r="D26" t="s">
         <v>81</v>
@@ -21309,13 +21309,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
         <v>162</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="D27" t="s">
         <v>81</v>
@@ -21326,19 +21326,19 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C28" t="n">
-        <v>5.62</v>
+        <v>6.44</v>
       </c>
       <c r="D28" t="s">
         <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -21346,101 +21346,101 @@
         <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C29" t="n">
-        <v>5.34</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
         <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C30" t="n">
-        <v>4.75</v>
+        <v>7.01</v>
       </c>
       <c r="D30" t="s">
         <v>81</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C31" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="D31" t="s">
         <v>81</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C32" t="n">
-        <v>6.27</v>
+        <v>4.25</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C33" t="n">
-        <v>5.84</v>
+        <v>4.95</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C34" t="n">
-        <v>4.56</v>
+        <v>5.62</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E34" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -21448,78 +21448,78 @@
         <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C35" t="n">
-        <v>4.81</v>
+        <v>6.18</v>
       </c>
       <c r="D35" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E35" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C36" t="n">
-        <v>5.55</v>
+        <v>5.34</v>
       </c>
       <c r="D36" t="s">
         <v>81</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C37" t="n">
-        <v>7.01</v>
+        <v>4.06</v>
       </c>
       <c r="D37" t="s">
         <v>81</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C38" t="n">
-        <v>6.18</v>
+        <v>6.01</v>
       </c>
       <c r="D38" t="s">
         <v>81</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
         <v>164</v>
       </c>
       <c r="C39" t="n">
-        <v>5.19</v>
+        <v>5.34</v>
       </c>
       <c r="D39" t="s">
         <v>81</v>
@@ -21533,101 +21533,101 @@
         <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" t="n">
-        <v>6.17</v>
+        <v>5.19</v>
       </c>
       <c r="D40" t="s">
         <v>81</v>
       </c>
       <c r="E40" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C41" t="n">
-        <v>5.13</v>
+        <v>5.51</v>
       </c>
       <c r="D41" t="s">
         <v>81</v>
       </c>
       <c r="E41" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B42" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="C42" t="n">
-        <v>6.04</v>
+        <v>5.05</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>6.38</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C44" t="n">
-        <v>4.18</v>
+        <v>4.75</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E44" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C45" t="n">
-        <v>5.81</v>
+        <v>6.17</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="E45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46">
@@ -21635,84 +21635,84 @@
         <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C46" t="n">
-        <v>5.07</v>
+        <v>5.85</v>
       </c>
       <c r="D46" t="s">
         <v>81</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C47" t="n">
-        <v>5.15</v>
+        <v>4.73</v>
       </c>
       <c r="D47" t="s">
         <v>81</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C48" t="n">
-        <v>5.34</v>
+        <v>5.45</v>
       </c>
       <c r="D48" t="s">
         <v>81</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B49" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C49" t="n">
-        <v>5.51</v>
+        <v>4.95</v>
       </c>
       <c r="D49" t="s">
         <v>81</v>
       </c>
       <c r="E49" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C50" t="n">
-        <v>5.85</v>
+        <v>5.13</v>
       </c>
       <c r="D50" t="s">
         <v>81</v>
       </c>
       <c r="E50" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -21800,94 +21800,94 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="D3" t="s">
         <v>81</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.05</v>
+        <v>6.4</v>
       </c>
       <c r="G3" t="n">
-        <v>-46.0992907801418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C4" t="n">
-        <v>4.25</v>
+        <v>5.81</v>
       </c>
       <c r="D4" t="s">
         <v>81</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.05</v>
+        <v>5.81</v>
       </c>
       <c r="G4" t="n">
-        <v>-39.7163120567376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C5" t="n">
-        <v>4.06</v>
+        <v>5.55</v>
       </c>
       <c r="D5" t="s">
         <v>81</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>7.05</v>
+        <v>5.55</v>
       </c>
       <c r="G5" t="n">
-        <v>-42.4113475177305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C6" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="D6" t="s">
         <v>81</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>7.05</v>
+        <v>5.07</v>
       </c>
       <c r="G6" t="n">
-        <v>-28.3687943262411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21895,22 +21895,22 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>4.73</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="s">
         <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>7.05</v>
       </c>
       <c r="G7" t="n">
-        <v>-32.9078014184397</v>
+        <v>-46.0992907801418</v>
       </c>
     </row>
     <row r="8">
@@ -21918,33 +21918,33 @@
         <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C8" t="n">
-        <v>6.4</v>
+        <v>6.44</v>
       </c>
       <c r="D8" t="s">
         <v>81</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>6.4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.625000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
         <v>162</v>
       </c>
       <c r="C9" t="n">
-        <v>6.44</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>81</v>
@@ -21953,79 +21953,79 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>6.4</v>
+        <v>5.81</v>
       </c>
       <c r="G9" t="n">
-        <v>0.625000000000001</v>
+        <v>20.4819277108434</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C10" t="n">
-        <v>4.95</v>
+        <v>7.01</v>
       </c>
       <c r="D10" t="s">
         <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6.4</v>
+        <v>5.55</v>
       </c>
       <c r="G10" t="n">
-        <v>-22.65625</v>
+        <v>26.3063063063063</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C11" t="n">
-        <v>6.01</v>
+        <v>5.15</v>
       </c>
       <c r="D11" t="s">
         <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>6.4</v>
+        <v>5.07</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.09375000000001</v>
+        <v>1.57790927021696</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" t="n">
-        <v>6.38</v>
+        <v>4.25</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>6.4</v>
+        <v>7.05</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.312500000000007</v>
+        <v>-39.7163120567376</v>
       </c>
     </row>
     <row r="13">
@@ -22033,22 +22033,22 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C13" t="n">
-        <v>5.45</v>
+        <v>4.95</v>
       </c>
       <c r="D13" t="s">
         <v>81</v>
       </c>
       <c r="E13" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>6.4</v>
       </c>
       <c r="G13" t="n">
-        <v>-14.84375</v>
+        <v>-22.65625</v>
       </c>
     </row>
     <row r="14">
@@ -22056,56 +22056,56 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" t="n">
-        <v>5.81</v>
+        <v>5.62</v>
       </c>
       <c r="D14" t="s">
         <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>5.81</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-3.27022375215145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>6.18</v>
       </c>
       <c r="D15" t="s">
         <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>5.81</v>
+        <v>5.55</v>
       </c>
       <c r="G15" t="n">
-        <v>20.4819277108434</v>
+        <v>11.3513513513513</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
         <v>163</v>
       </c>
       <c r="C16" t="n">
-        <v>5.62</v>
+        <v>5.34</v>
       </c>
       <c r="D16" t="s">
         <v>81</v>
@@ -22114,21 +22114,21 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>5.81</v>
+        <v>5.07</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.27022375215145</v>
+        <v>5.32544378698224</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>164</v>
       </c>
       <c r="C17" t="n">
-        <v>5.34</v>
+        <v>4.06</v>
       </c>
       <c r="D17" t="s">
         <v>81</v>
@@ -22137,33 +22137,33 @@
         <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>5.81</v>
+        <v>7.05</v>
       </c>
       <c r="G17" t="n">
-        <v>-8.08950086058519</v>
+        <v>-42.4113475177305</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C18" t="n">
-        <v>4.75</v>
+        <v>6.01</v>
       </c>
       <c r="D18" t="s">
         <v>81</v>
       </c>
       <c r="E18" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>5.81</v>
+        <v>6.4</v>
       </c>
       <c r="G18" t="n">
-        <v>-18.2444061962134</v>
+        <v>-6.09375000000001</v>
       </c>
     </row>
     <row r="19">
@@ -22171,22 +22171,22 @@
         <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C19" t="n">
-        <v>4.95</v>
+        <v>5.34</v>
       </c>
       <c r="D19" t="s">
         <v>81</v>
       </c>
       <c r="E19" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>5.81</v>
       </c>
       <c r="G19" t="n">
-        <v>-14.802065404475</v>
+        <v>-8.08950086058519</v>
       </c>
     </row>
     <row r="20">
@@ -22194,102 +22194,102 @@
         <v>57</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C20" t="n">
-        <v>5.55</v>
+        <v>5.19</v>
       </c>
       <c r="D20" t="s">
         <v>81</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
         <v>5.55</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-6.48648648648648</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C21" t="n">
-        <v>7.01</v>
+        <v>5.51</v>
       </c>
       <c r="D21" t="s">
         <v>81</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>5.55</v>
+        <v>5.07</v>
       </c>
       <c r="G21" t="n">
-        <v>26.3063063063063</v>
+        <v>8.67850098619328</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C22" t="n">
-        <v>6.18</v>
+        <v>5.05</v>
       </c>
       <c r="D22" t="s">
         <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
-        <v>5.55</v>
+        <v>7.05</v>
       </c>
       <c r="G22" t="n">
-        <v>11.3513513513513</v>
+        <v>-28.3687943262411</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" t="n">
-        <v>5.19</v>
+        <v>6.38</v>
       </c>
       <c r="D23" t="s">
         <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>5.55</v>
+        <v>6.4</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.48648648648648</v>
+        <v>-0.312500000000007</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
         <v>165</v>
       </c>
       <c r="C24" t="n">
-        <v>6.17</v>
+        <v>4.75</v>
       </c>
       <c r="D24" t="s">
         <v>81</v>
@@ -22298,10 +22298,10 @@
         <v>21</v>
       </c>
       <c r="F24" t="n">
-        <v>5.55</v>
+        <v>5.81</v>
       </c>
       <c r="G24" t="n">
-        <v>11.1711711711712</v>
+        <v>-18.2444061962134</v>
       </c>
     </row>
     <row r="25">
@@ -22309,22 +22309,22 @@
         <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" t="n">
-        <v>5.13</v>
+        <v>6.17</v>
       </c>
       <c r="D25" t="s">
         <v>81</v>
       </c>
       <c r="E25" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F25" t="n">
         <v>5.55</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.56756756756757</v>
+        <v>11.1711711711712</v>
       </c>
     </row>
     <row r="26">
@@ -22332,114 +22332,114 @@
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C26" t="n">
-        <v>5.07</v>
+        <v>5.85</v>
       </c>
       <c r="D26" t="s">
         <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F26" t="n">
         <v>5.07</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>15.3846153846154</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C27" t="n">
-        <v>5.15</v>
+        <v>4.73</v>
       </c>
       <c r="D27" t="s">
         <v>81</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F27" t="n">
-        <v>5.07</v>
+        <v>7.05</v>
       </c>
       <c r="G27" t="n">
-        <v>1.57790927021696</v>
+        <v>-32.9078014184397</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C28" t="n">
-        <v>5.34</v>
+        <v>5.45</v>
       </c>
       <c r="D28" t="s">
         <v>81</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="F28" t="n">
-        <v>5.07</v>
+        <v>6.4</v>
       </c>
       <c r="G28" t="n">
-        <v>5.32544378698224</v>
+        <v>-14.84375</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C29" t="n">
-        <v>5.51</v>
+        <v>4.95</v>
       </c>
       <c r="D29" t="s">
         <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F29" t="n">
-        <v>5.07</v>
+        <v>5.81</v>
       </c>
       <c r="G29" t="n">
-        <v>8.67850098619328</v>
+        <v>-14.802065404475</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" t="n">
-        <v>5.85</v>
+        <v>5.13</v>
       </c>
       <c r="D30" t="s">
         <v>81</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
-        <v>5.07</v>
+        <v>5.55</v>
       </c>
       <c r="G30" t="n">
-        <v>15.3846153846154</v>
+        <v>-7.56756756756757</v>
       </c>
     </row>
     <row r="31">
